--- a/Tests/representative_network_3_sim_outputs.xlsx
+++ b/Tests/representative_network_3_sim_outputs.xlsx
@@ -1,37 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -330,10 +385,309 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1" t="n">
+        <v>51</v>
+      </c>
+      <c r="C1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G1" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I1" t="n">
+        <v>7412.811605589501</v>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K1" t="n">
+        <v>1347.257758706808</v>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M1" t="n">
+        <v>29584.09241321683</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5219.49406864807</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1102.261436428875</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>7012.928060732665</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>51</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5132.900601074565</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>3304.590491615236</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>6423.440535143018</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>51</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>7248.614433126233</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>3019.39438380301</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>17113.41414250946</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>51</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4804.271060830086</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1212.639057680964</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>6875.454712001607</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>51</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4873.948528671067</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2118.125667039305</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>12026.20588560775</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>